--- a/Резерв_ПВЗ_Орск_15.10-25.12.2026.xlsx
+++ b/Резерв_ПВЗ_Орск_15.10-25.12.2026.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Таблица владельца" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Кредит" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Личные финансы" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Допущения и вопросы" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Второй ПВЗ (оценка)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Допущения и вопросы" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -163,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -285,6 +286,33 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -1136,8 +1164,15 @@
         </is>
       </c>
     </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>• Оценка покупки второго ПВЗ (100–120 привозов/день) и ориентир его цены — отдельный лист «Второй ПВЗ (оценка)».</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B8:D8"/>
@@ -1158,6 +1193,7 @@
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4937,6 +4973,856 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ОЦЕНКА ВТОРОГО ПВЗ (привоз 100–120 товаров/день)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Расчёт — экстраполяция экономики вашего ПВЗ на меньший объём: ставки и структура расходов взяты из ваших данных, объём и часть статей расходов масштабируются. Жёлтые ячейки — ввод. Это модель для переговоров, не факт: реальные цифры берутся из кабинета Ozon владельца точки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1. ОБЪЁМ И ВОЗНАГРАЖДЕНИЕ (масштаб от вашего ПВЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B5" s="44" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>Привоз, товаров/день</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="F6" s="46" t="inlineStr">
+        <is>
+          <t>У вашего ПВЗ ~250/день; у рассматриваемой точки 100–120</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>Тариф drop-off, ₽/товар</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="46" t="inlineStr">
+        <is>
+          <t>Ваша модель: 250 × 10 ₽ × 30 = 75 000 ₽; факт Q3 = 77 836 ₽ (≈10,4 ₽/товар)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>Выдач на 1 привезённый товар</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F8" s="46" t="inlineStr">
+        <is>
+          <t>У вас: ~5 700–5 800 выдач при ~7 500 привозов в месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>Тариф выдачи, ₽ за выдачу</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="F9" s="46" t="inlineStr">
+        <is>
+          <t>Факт Q3: 131 760 ₽ / 5 750 выдач</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Drop-off, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B10" s="32">
+        <f>B6*30*B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>Выдач, шт/мес</t>
+        </is>
+      </c>
+      <c r="B11" s="48">
+        <f>B6*30*B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Выдача, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B12" s="32">
+        <f>B11*B9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="45" t="inlineStr">
+        <is>
+          <t>Прочие категории, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B13" s="32">
+        <f>B6/250*31911.31</f>
+        <v/>
+      </c>
+      <c r="F13" s="46" t="inlineStr">
+        <is>
+          <t>Пропорционально объёму (Q3 у вас: 31 911 ₽/мес; сверить с актами)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>ВОЗНАГРАЖДЕНИЕ, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B14" s="33">
+        <f>B10+B12+B13</f>
+        <v/>
+      </c>
+      <c r="F14" s="46" t="inlineStr">
+        <is>
+          <t>Проверка: 241 507 ₽ × (110/250) ≈ 106 263 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2. РАСХОДЫ ТОЧКИ (ввод)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="45" t="inlineStr">
+        <is>
+          <t>Аренда, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F17" s="46" t="inlineStr">
+        <is>
+          <t>У вас 42 000; у маленькой точки обычно меньше — уточнить по договору</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="45" t="inlineStr">
+        <is>
+          <t>Электричество, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B18" s="34" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>Интернет, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="45" t="inlineStr">
+        <is>
+          <t>Камеры, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
+        <is>
+          <t>Cashback селлерам, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B21" s="35">
+        <f>B6/250*1000*30</f>
+        <v/>
+      </c>
+      <c r="F21" s="46" t="inlineStr">
+        <is>
+          <t>Масштабируется от объёма: 1 000 ₽/день у вас при 250 привозов (здесь 440 ₽/день × 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="45" t="inlineStr">
+        <is>
+          <t>Сотрудников, чел.</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="46" t="inlineStr">
+        <is>
+          <t>Ключевой параметр: при 100–120 привозов/день точка тянет одного сотрудника</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Зарплата на руки, ₽/мес на человека</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="n">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>3. ПЕРСОНАЛ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>Gross ФОТ (с НДФЛ 13%)</t>
+        </is>
+      </c>
+      <c r="B26" s="32">
+        <f>B22*B23/(1-0.13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="45" t="inlineStr">
+        <is>
+          <t>Страховые взносы 30%</t>
+        </is>
+      </c>
+      <c r="B27" s="32">
+        <f>B26*0.3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="45" t="inlineStr">
+        <is>
+          <t>Травматизм (300 ₽/чел.)</t>
+        </is>
+      </c>
+      <c r="B28" s="35">
+        <f>B22*300</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="45" t="inlineStr">
+        <is>
+          <t>Полная стоимость ФОТ (УСН)</t>
+        </is>
+      </c>
+      <c r="B29" s="33">
+        <f>B26+B27+B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="45" t="inlineStr">
+        <is>
+          <t>Персонал на АУСН (только gross)</t>
+        </is>
+      </c>
+      <c r="B30" s="32">
+        <f>B26</f>
+        <v/>
+      </c>
+      <c r="F30" s="46" t="inlineStr">
+        <is>
+          <t>На АУСН взносы за сотрудников 0% — для маленькой точки это решающая экономия</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>4. НАЛОГИ И ВЗНОСЫ ИП (точка отдельным ИП)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>АУСН 8%</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>УСН 6%</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>Ставка налога</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C34" s="42" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="inlineStr">
+        <is>
+          <t>Налог до уменьшения</t>
+        </is>
+      </c>
+      <c r="B35" s="32">
+        <f>$B$14*B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="32">
+        <f>$B$14*C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="45" t="inlineStr">
+        <is>
+          <t>Уменьшение налога взносами (≤50%)</t>
+        </is>
+      </c>
+      <c r="C36" s="32">
+        <f>MIN(4782.5+($B$14*12-300000)*0.01/12+B27+B28,C35*0.5)</f>
+        <v/>
+      </c>
+      <c r="F36" s="46" t="inlineStr">
+        <is>
+          <t>Свои взносы (4 782,50 + 1%) + взносы за сотрудника; лимит 50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="inlineStr">
+        <is>
+          <t>ВНиМ ИП (АУСН, 2 959 ₽/год)</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n">
+        <v>246.58</v>
+      </c>
+      <c r="C37" s="32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="49" t="inlineStr">
+        <is>
+          <t>Итого налоги и взносы ИП, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B38" s="33">
+        <f>B35+B37</f>
+        <v/>
+      </c>
+      <c r="C38" s="33">
+        <f>C35-C36+4782.5+($B$14*12-300000)*0.01/12</f>
+        <v/>
+      </c>
+      <c r="F38" s="46" t="inlineStr">
+        <is>
+          <t>УСН: налог после уменьшения + фиксвзносы 4 782,50 + 1% свыше 300 000 ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>5. ИТОГО: ПРИБЫЛЬ ТОЧКИ ПРИ РАЗНЫХ УСЛОВИЯХ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Показатель</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>АУСН, 1 сотрудник</t>
+        </is>
+      </c>
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>УСН, 1 сотрудник</t>
+        </is>
+      </c>
+      <c r="D41" s="44" t="inlineStr">
+        <is>
+          <t>АУСН, 2 сотрудника</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="inlineStr">
+        <is>
+          <t>УСН, 2 сотрудника</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="45" t="inlineStr">
+        <is>
+          <t>Постоянные расходы (аренда, камеры, интернет, свет, cashback)</t>
+        </is>
+      </c>
+      <c r="B42" s="32">
+        <f>SUM(B17:B21)</f>
+        <v/>
+      </c>
+      <c r="C42" s="32">
+        <f>SUM(B17:B21)</f>
+        <v/>
+      </c>
+      <c r="D42" s="32">
+        <f>SUM(B17:B21)</f>
+        <v/>
+      </c>
+      <c r="E42" s="32">
+        <f>SUM(B17:B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="45" t="inlineStr">
+        <is>
+          <t>Персонал</t>
+        </is>
+      </c>
+      <c r="B43" s="32">
+        <f>B30</f>
+        <v/>
+      </c>
+      <c r="C43" s="32">
+        <f>B29</f>
+        <v/>
+      </c>
+      <c r="D43" s="32">
+        <f>B30/B22*2</f>
+        <v/>
+      </c>
+      <c r="E43" s="32">
+        <f>B29/B22*2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="inlineStr">
+        <is>
+          <t>Налоги и взносы ИП</t>
+        </is>
+      </c>
+      <c r="B44" s="32">
+        <f>B38</f>
+        <v/>
+      </c>
+      <c r="C44" s="32">
+        <f>C38</f>
+        <v/>
+      </c>
+      <c r="D44" s="32">
+        <f>B38</f>
+        <v/>
+      </c>
+      <c r="E44" s="32">
+        <f>C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="49" t="inlineStr">
+        <is>
+          <t>ИТОГО расходов, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B45" s="33">
+        <f>B42+B43+B44</f>
+        <v/>
+      </c>
+      <c r="C45" s="33">
+        <f>C42+C43+C44</f>
+        <v/>
+      </c>
+      <c r="D45" s="33">
+        <f>D42+D43+D44</f>
+        <v/>
+      </c>
+      <c r="E45" s="33">
+        <f>E42+E43+E44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="45" t="inlineStr">
+        <is>
+          <t>Вознаграждение Ozon, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B46" s="32">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="C46" s="32">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="D46" s="32">
+        <f>$B$14</f>
+        <v/>
+      </c>
+      <c r="E46" s="32">
+        <f>$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="49" t="inlineStr">
+        <is>
+          <t>ПРИБЫЛЬ, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B47" s="33">
+        <f>B46-B45</f>
+        <v/>
+      </c>
+      <c r="C47" s="33">
+        <f>C46-C45</f>
+        <v/>
+      </c>
+      <c r="D47" s="33">
+        <f>D46-D45</f>
+        <v/>
+      </c>
+      <c r="E47" s="33">
+        <f>E46-E45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>6. ОРИЕНТИР ЦЕНЫ ПОКУПКИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="45" t="inlineStr">
+        <is>
+          <t>Мультипликатор вашей сделки (мес. вознаграждения)</t>
+        </is>
+      </c>
+      <c r="B50" s="50" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F50" s="46" t="inlineStr">
+        <is>
+          <t>675 000 ₽ / 241 507 ₽ = 2,8 мес. вознаграждения</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="45" t="inlineStr">
+        <is>
+          <t>Цена по мультипликатору (2,8 × вознаграждение)</t>
+        </is>
+      </c>
+      <c r="B51" s="35">
+        <f>B14*B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>Цена по прибыли, 12 мес. (АУСН, 1 сотрудник)</t>
+        </is>
+      </c>
+      <c r="B52" s="35">
+        <f>B47*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="45" t="inlineStr">
+        <is>
+          <t>Цена по прибыли, 18 мес. (АУСН, 1 сотрудник)</t>
+        </is>
+      </c>
+      <c r="B53" s="35">
+        <f>B47*18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="51" t="inlineStr">
+        <is>
+          <t>ВЫВОД: ориентир цены ≈ 150 000 – 300 000 ₽ — только при 1 сотруднике и АУСН и подтверждённых цифрах кабинета. При двух сотрудниках точка убыточна — покупать нельзя (цена = стоимость оборудования).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>7. СТРЕСС-ТЕСТ: МИНУС 30% ОБЪЁМА (72 привоза/день)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="45" t="inlineStr">
+        <is>
+          <t>Вознаграждение, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B58" s="32">
+        <f>B14*0.7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="45" t="inlineStr">
+        <is>
+          <t>Расходы (АУСН, 1 сотрудник; cashback тоже падает)</t>
+        </is>
+      </c>
+      <c r="B59" s="32">
+        <f>B17+B18+B19+B20+B21*0.7+B30+B35*0.7+B37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="49" t="inlineStr">
+        <is>
+          <t>Прибыль, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B60" s="33">
+        <f>B58-B59</f>
+        <v/>
+      </c>
+      <c r="F60" s="46" t="inlineStr">
+        <is>
+          <t>У вашего ПВЗ drop-off за год был от 59 477 до 181 365 ₽/мес — сезонность реальна</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>8. ЧТО ПРОВЕРИТЬ ПЕРЕД ПОКУПКОЙ (может собрать жена, работая там)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="52" t="inlineStr">
+        <is>
+          <t>1. Скриншоты вознаграждения из кабинета Ozon за 6–12 месяцев: не среднее, а тренд и сезонность.</t>
+        </is>
+      </c>
+      <c r="B63" s="30" t="n"/>
+      <c r="C63" s="30" t="n"/>
+      <c r="D63" s="30" t="n"/>
+      <c r="E63" s="30" t="n"/>
+      <c r="F63" s="31" t="n"/>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="52" t="inlineStr">
+        <is>
+          <t>2. Фактическое число выдач и привозов в день, количество активных селлеров, долги по cashback (типичная скрытая ответственность при покупке ПВЗ).</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="n"/>
+      <c r="C64" s="30" t="n"/>
+      <c r="D64" s="30" t="n"/>
+      <c r="E64" s="30" t="n"/>
+      <c r="F64" s="31" t="n"/>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="52" t="inlineStr">
+        <is>
+          <t>3. Договор аренды: срок, ставка, долги; рейтинг и штрафы в кабинете Ozon; состояние оборудования (стеллажи, ПК, сканеры, камеры).</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="n"/>
+      <c r="C65" s="30" t="n"/>
+      <c r="D65" s="30" t="n"/>
+      <c r="E65" s="30" t="n"/>
+      <c r="F65" s="31" t="n"/>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="52" t="inlineStr">
+        <is>
+          <t>4. Почему продают и на каких условиях передаётся договор с Ozon — только официальная переоформка, не «теневая» передача.</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="n"/>
+      <c r="C66" s="30" t="n"/>
+      <c r="D66" s="30" t="n"/>
+      <c r="E66" s="30" t="n"/>
+      <c r="F66" s="31" t="n"/>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="52" t="inlineStr">
+        <is>
+          <t>5. Можно ли одному ИП держать два ПВЗ — уточнить у менеджера Ozon; на одном ИП фиксированные взносы одни (экономия ~4 783 ₽/мес на второй точке).</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="n"/>
+      <c r="C67" s="30" t="n"/>
+      <c r="D67" s="30" t="n"/>
+      <c r="E67" s="30" t="n"/>
+      <c r="F67" s="31" t="n"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="52" t="inlineStr">
+        <is>
+          <t>6. АУСН для второй точки критичен: экономия взносов за персонал ~9 600 ₽/мес — именно она превращает минус в плюс при одном сотруднике.</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="n"/>
+      <c r="C68" s="30" t="n"/>
+      <c r="D68" s="30" t="n"/>
+      <c r="E68" s="30" t="n"/>
+      <c r="F68" s="31" t="n"/>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="52" t="inlineStr">
+        <is>
+          <t>7. Резерв: вторая точка на старте тоже требует денег (ориентировочно 150–250 тыс. ₽) — они конкурируют с резервом первой точки и платежами по кредиту 923 000 ₽.</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="n"/>
+      <c r="C69" s="30" t="n"/>
+      <c r="D69" s="30" t="n"/>
+      <c r="E69" s="30" t="n"/>
+      <c r="F69" s="31" t="n"/>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="52" t="inlineStr">
+        <is>
+          <t>8. Альтернатива без риска: жена работает там за 27 000 ₽/мес, собирает реальные цифры 2–3 месяца — и тогда торг с фактами, а не со словами продавца.</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="n"/>
+      <c r="C70" s="30" t="n"/>
+      <c r="D70" s="30" t="n"/>
+      <c r="E70" s="30" t="n"/>
+      <c r="F70" s="31" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A65:F65"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
